--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_318_R32.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_318_R32.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9905</v>
+        <v>6.6362</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1469</v>
+        <v>5.9607</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8435</v>
+        <v>0.6755</v>
       </c>
       <c r="G2" t="n">
         <v>7.2861</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7569</v>
+        <v>-0.1111</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1949</v>
+        <v>-0.3811</v>
       </c>
       <c r="U2" t="n">
-        <v>0.438</v>
+        <v>0.27</v>
       </c>
       <c r="V2" t="n">
         <v>-1.4665</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6663</v>
+        <v>3.2697</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3513</v>
+        <v>2.6186</v>
       </c>
       <c r="F3" t="n">
-        <v>0.315</v>
+        <v>0.6511</v>
       </c>
       <c r="G3" t="n">
         <v>0.6425999999999999</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9041</v>
+        <v>-0.3007</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4007</v>
+        <v>-0.1333</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5034</v>
+        <v>-0.1674</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2941</v>
+        <v>1.5409</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8016</v>
+        <v>0.082</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4925</v>
+        <v>1.4589</v>
       </c>
       <c r="G4" t="n">
         <v>3.6589</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7639</v>
+        <v>0.0108</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0227</v>
+        <v>0.3031</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2587</v>
+        <v>-0.2923</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5051</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>B. ANGOLA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2849</v>
+        <v>0.5668</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2667</v>
+        <v>-0.2158</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0182</v>
+        <v>0.7826</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1509</v>
+        <v>0.2414</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1849</v>
+        <v>1.3289</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0341</v>
+        <v>-1.0874</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0066</v>
+        <v>0.7098</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8767</v>
+        <v>1.5832</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8833</v>
+        <v>-0.8734</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1575</v>
+        <v>-0.4683</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3082</v>
+        <v>-0.2543</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1507</v>
+        <v>-0.214</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3482</v>
+        <v>-0.8011</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6518</v>
+        <v>-0.6603</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3035</v>
+        <v>-0.1408</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.6083</v>
+        <v>2.2862</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. ANGOLA</t>
+          <t>S. HARRISON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1479</v>
+        <v>-1.0152</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6011</v>
+        <v>0.0043</v>
       </c>
       <c r="F6" t="n">
-        <v>0.749</v>
+        <v>-1.0195</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2414</v>
+        <v>-1.7848</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3289</v>
+        <v>-1.4202</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0874</v>
+        <v>-0.3647</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7098</v>
+        <v>-0.6052</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5832</v>
+        <v>-0.7156</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8734</v>
+        <v>0.1104</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4683</v>
+        <v>-1.1796</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2543</v>
+        <v>-0.7045</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.214</v>
+        <v>-0.4751</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2199</v>
+        <v>0.3058</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0455</v>
+        <v>0.6095</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1744</v>
+        <v>-0.3038</v>
       </c>
       <c r="V6" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5051</v>
+        <v>-1.1028</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.5356</v>
+        <v>-2.0323</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0304</v>
+        <v>0.9296</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2596</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7121</v>
+        <v>-0.3097</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4481</v>
+        <v>0.0551</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.264</v>
+        <v>-0.3648</v>
       </c>
       <c r="V7" t="n">
         <v>0.3943</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. HARRISON</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.091</v>
+        <v>-1.1999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9707</v>
+        <v>-1.1173</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1203</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7848</v>
+        <v>-0.1509</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4202</v>
+        <v>-1.1849</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3647</v>
+        <v>1.0341</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6052</v>
+        <v>0.0066</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7156</v>
+        <v>-0.8767</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1104</v>
+        <v>0.8833</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1796</v>
+        <v>-0.1575</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7045</v>
+        <v>-0.3082</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4751</v>
+        <v>0.1507</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7701</v>
+        <v>-0.1366</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3655</v>
+        <v>0.2677</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4046</v>
+        <v>-0.4044</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>E. JACKSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6323</v>
+        <v>-2.5783</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5265</v>
+        <v>-1.12</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1058</v>
+        <v>-1.4584</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8611</v>
+        <v>1.0202</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2654</v>
+        <v>0.2606</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5957</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2332</v>
+        <v>0.3877</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1595</v>
+        <v>-0.1141</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0736</v>
+        <v>0.5018</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3721</v>
+        <v>0.6325</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8942</v>
+        <v>0.3748</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5221</v>
+        <v>0.2578</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8804</v>
+        <v>-0.8975</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4402</v>
+        <v>-0.6289</v>
       </c>
       <c r="U9" t="n">
-        <v>1.3205</v>
+        <v>-0.2686</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.2862</v>
+        <v>-2.933</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6468</v>
       </c>
       <c r="X9" t="n">
         <v>-2.2862</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. JACKSON</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.066</v>
+        <v>-2.8012</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2379</v>
+        <v>-1.0233</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.828</v>
+        <v>-1.7779</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0202</v>
+        <v>0.8611</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2606</v>
+        <v>0.2654</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.5957</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3877</v>
+        <v>1.2332</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1141</v>
+        <v>1.1595</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5018</v>
+        <v>0.0736</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6325</v>
+        <v>-0.3721</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3748</v>
+        <v>-0.8942</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2578</v>
+        <v>0.5221</v>
       </c>
       <c r="P10" t="n">
+        <v>-2.0876</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-2.3195</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.232</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.4639</v>
-      </c>
       <c r="S10" t="n">
-        <v>-1.3851</v>
+        <v>0.7114</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7468</v>
+        <v>0.063</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6383</v>
+        <v>0.6484</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.933</v>
+        <v>-2.2862</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6468</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-2.2862</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0619</v>
+        <v>-3.1115</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1885</v>
+        <v>-2.4061</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8734</v>
+        <v>-0.7054</v>
       </c>
       <c r="G11" t="n">
         <v>-3.3369</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0987</v>
+        <v>-0.1483</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7389</v>
+        <v>0.0435</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3598</v>
+        <v>-0.1918</v>
       </c>
       <c r="V11" t="n">
         <v>0.1418</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.2632</v>
+        <v>-4.947</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5173</v>
+        <v>-2.2683</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7459</v>
+        <v>-2.6787</v>
       </c>
       <c r="G12" t="n">
         <v>-4.6054</v>
@@ -1390,13 +1390,13 @@
         <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7881</v>
+        <v>0.1043</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9006</v>
+        <v>0.1496</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6778999999999999</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.235799999999999</v>
+        <v>-4.742300000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.011100000000001</v>
+        <v>-1.517500000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-3.2248</v>
@@ -1435,19 +1435,19 @@
         <v>3.5727</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.466699999999999</v>
+        <v>-2.4667</v>
       </c>
       <c r="I13" t="n">
         <v>6.039599999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>8.525700000000002</v>
+        <v>8.525700000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>4.277399999999999</v>
+        <v>4.277400000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>4.248200000000001</v>
+        <v>4.248199999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-4.9529</v>
@@ -1459,7 +1459,7 @@
         <v>1.7912</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.159700000000001</v>
+        <v>-1.1597</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.7575</v>
@@ -1468,10 +1468,10 @@
         <v>11.5978</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.0663</v>
+        <v>-1.5727</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.8055</v>
+        <v>-0.3120999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>-1.2607</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4224</v>
+        <v>6.9449</v>
       </c>
       <c r="E14" t="n">
-        <v>5.9249</v>
+        <v>6.5146</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4975</v>
+        <v>0.4303</v>
       </c>
       <c r="G14" t="n">
         <v>6.1922</v>
@@ -1546,13 +1546,13 @@
         <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6976</v>
+        <v>-0.1751</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6642</v>
+        <v>-0.0745</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0334</v>
+        <v>-0.1006</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.3749</v>
+        <v>4.5531</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1846</v>
+        <v>2.7955</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1903</v>
+        <v>1.7576</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5101</v>
+        <v>1.8347</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0552</v>
+        <v>0.754</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.455</v>
+        <v>1.0807</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3781</v>
+        <v>1.8096</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2505</v>
+        <v>0.6722</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1275</v>
+        <v>1.1374</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.8882</v>
+        <v>0.025</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3057</v>
+        <v>0.0818</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5825</v>
+        <v>-0.0568</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>3.3826</v>
+        <v>0.0716</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9663</v>
+        <v>-0.0863</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4163</v>
+        <v>0.1579</v>
       </c>
       <c r="V15" t="n">
-        <v>0.1107</v>
+        <v>1.719</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1107</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1428</v>
+        <v>2.7477</v>
       </c>
       <c r="E16" t="n">
-        <v>2.4417</v>
+        <v>2.0051</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7012</v>
+        <v>0.7427</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8347</v>
+        <v>-0.5101</v>
       </c>
       <c r="H16" t="n">
-        <v>0.754</v>
+        <v>-0.0552</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0807</v>
+        <v>-0.455</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8096</v>
+        <v>2.3781</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6722</v>
+        <v>1.2505</v>
       </c>
       <c r="L16" t="n">
-        <v>1.1374</v>
+        <v>1.1275</v>
       </c>
       <c r="M16" t="n">
-        <v>0.025</v>
+        <v>-2.8882</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0818</v>
+        <v>-1.3057</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0568</v>
+        <v>-1.5825</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3387</v>
+        <v>1.7554</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4402</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1015</v>
+        <v>0.9687</v>
       </c>
       <c r="V16" t="n">
-        <v>1.719</v>
+        <v>0.1107</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6468</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4375</v>
+        <v>1.8649</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3536</v>
+        <v>0.8818</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0839</v>
+        <v>0.9831</v>
       </c>
       <c r="G17" t="n">
         <v>1.5259</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6049</v>
+        <v>0.0323</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5623</v>
+        <v>0.0905</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0426</v>
+        <v>-0.0582</v>
       </c>
       <c r="V17" t="n">
         <v>1.4665</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1936</v>
+        <v>1.5183</v>
       </c>
       <c r="E18" t="n">
-        <v>0.138</v>
+        <v>-0.0979</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0557</v>
+        <v>1.6162</v>
       </c>
       <c r="G18" t="n">
         <v>-3.1744</v>
@@ -1858,13 +1858,13 @@
         <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4736</v>
+        <v>0.7982</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4683</v>
+        <v>0.2324</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0053</v>
+        <v>0.5658</v>
       </c>
       <c r="V18" t="n">
         <v>3.8945</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7824</v>
+        <v>-0.4115</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9802</v>
+        <v>-0.5084</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1977</v>
+        <v>0.0969</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5318</v>
@@ -1936,13 +1936,13 @@
         <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.4158</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6721</v>
+        <v>-0.2003</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1147</v>
+        <v>-0.2155</v>
       </c>
       <c r="V19" t="n">
         <v>1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>L. WALKER IV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6205</v>
+        <v>-1.4888</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3641</v>
+        <v>-3.0627</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2564</v>
+        <v>1.5739</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2176</v>
+        <v>-4.8423</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3745</v>
+        <v>-1.7874</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8431</v>
+        <v>-3.0549</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7023</v>
+        <v>-3.8482</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7023</v>
+        <v>-0.8501</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-2.9982</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5153</v>
+        <v>-0.9941</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6722</v>
+        <v>-0.9373</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8431</v>
+        <v>-0.0568</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7415</v>
+        <v>0.4257</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3383</v>
+        <v>-0.2867</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4033</v>
+        <v>0.7123</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. WALKER IV</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7742</v>
+        <v>-1.9236</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8884</v>
+        <v>-0.6</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1142</v>
+        <v>-1.3237</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.8423</v>
+        <v>-2.2176</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7874</v>
+        <v>-1.3745</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.0549</v>
+        <v>-0.8431</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.8482</v>
+        <v>-0.7023</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8501</v>
+        <v>-0.7023</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.9982</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9941</v>
+        <v>-1.5153</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9373</v>
+        <v>-0.6722</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0568</v>
+        <v>-0.8431</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8597</v>
+        <v>0.4384</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1123</v>
+        <v>0.1024</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2526</v>
+        <v>0.3361</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0091</v>
+        <v>-2.7402</v>
       </c>
       <c r="E22" t="n">
         <v>-2.8527</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1564</v>
+        <v>0.1124</v>
       </c>
       <c r="G22" t="n">
         <v>-0.397</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2926</v>
+        <v>-0.0237</v>
       </c>
       <c r="T22" t="n">
         <v>0.13</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4226</v>
+        <v>-0.1537</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1492</v>
+        <v>-4.0427</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3384</v>
+        <v>-1.4563</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8108</v>
+        <v>-2.5863</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4521</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8391</v>
+        <v>0.9456</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6844</v>
+        <v>0.5665</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1546</v>
+        <v>0.3791</v>
       </c>
       <c r="V23" t="n">
         <v>-2.6805</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.235800000000001</v>
+        <v>7.022099999999998</v>
       </c>
       <c r="E24" t="n">
-        <v>3.619000000000002</v>
+        <v>3.619000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>2.616900000000001</v>
+        <v>3.4031</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5725</v>
@@ -2326,16 +2326,16 @@
         <v>12.7574</v>
       </c>
       <c r="S24" t="n">
-        <v>3.0663</v>
+        <v>3.852600000000001</v>
       </c>
       <c r="T24" t="n">
         <v>1.2608</v>
       </c>
       <c r="U24" t="n">
-        <v>1.8055</v>
+        <v>2.5919</v>
       </c>
       <c r="V24" t="n">
-        <v>5.5824</v>
+        <v>5.582399999999998</v>
       </c>
       <c r="W24" t="n">
         <v>9.003</v>
